--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -627,7 +627,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-radiology-findings.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-observation-radiology-findings.xlsx
@@ -655,6 +655,14 @@
     <t>このObservationを分類するコード。(imaging)が指定される。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="imaging"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -809,9 +817,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>imaging</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -1345,7 +1350,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -3893,7 +3898,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3912,7 +3917,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3965,10 +3970,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3991,13 +3996,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4048,7 +4053,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4072,7 +4077,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4083,10 +4088,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4115,7 +4120,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4156,10 +4161,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4168,7 +4173,7 @@
         <v>196</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4192,7 +4197,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4203,10 +4208,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4229,19 +4234,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4290,7 +4295,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4311,10 +4316,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4325,10 +4330,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4351,13 +4356,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4408,7 +4413,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4432,7 +4437,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4443,10 +4448,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4475,7 +4480,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4516,10 +4521,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4528,7 +4533,7 @@
         <v>196</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4552,7 +4557,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4563,10 +4568,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4592,23 +4597,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4650,7 +4655,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4671,10 +4676,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4685,10 +4690,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4711,16 +4716,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4770,7 +4775,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4791,10 +4796,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4805,10 +4810,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4834,21 +4839,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4951,7 +4956,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>261</v>
@@ -5193,7 +5198,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>279</v>
@@ -5437,13 +5442,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5494,7 +5499,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5518,7 +5523,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5561,7 +5566,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5602,10 +5607,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5614,7 +5619,7 @@
         <v>196</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5638,7 +5643,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5675,19 +5680,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5736,7 +5741,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5757,10 +5762,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5797,13 +5802,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5854,7 +5859,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5878,7 +5883,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5921,7 +5926,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5962,10 +5967,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -5974,7 +5979,7 @@
         <v>196</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5998,7 +6003,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6038,16 +6043,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6096,7 +6101,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6117,10 +6122,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6157,16 +6162,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6216,7 +6221,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6237,10 +6242,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6280,14 +6285,14 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6397,7 +6402,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>261</v>
@@ -6639,7 +6644,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>279</v>
@@ -7489,7 +7494,7 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>364</v>
@@ -8581,13 +8586,13 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8638,7 +8643,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8662,7 +8667,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8705,7 +8710,7 @@
         <v>141</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -8758,7 +8763,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8782,7 +8787,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9541,7 +9546,7 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>481</v>
@@ -10021,13 +10026,13 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10078,7 +10083,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10102,7 +10107,7 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10145,7 +10150,7 @@
         <v>141</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -10198,7 +10203,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10222,7 +10227,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
